--- a/data/trans_orig/IP3108-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3108-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>722</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82174</t>
+          <t>82510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90979</t>
+          <t>90909</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76689</t>
+          <t>77549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85877</t>
+          <t>85836</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162981</t>
+          <t>162467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>174690</t>
+          <t>175057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67326</t>
+          <t>67250</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75318</t>
+          <t>75517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70679</t>
+          <t>70328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78169</t>
+          <t>78182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141036</t>
+          <t>140856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151851</t>
+          <t>151747</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1646</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8598</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4393</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49231</t>
+          <t>48753</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58667</t>
+          <t>58465</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78648</t>
+          <t>78680</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89182</t>
+          <t>88557</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>131160</t>
+          <t>130983</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145000</t>
+          <t>145461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3385</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,42 +3172,42 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>8673</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>4373</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>14464</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>3,87%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>8673</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>4806</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>14016</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>167520</t>
+          <t>167597</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>178582</t>
+          <t>179254</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167213</t>
+          <t>167488</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>178310</t>
+          <t>178175</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>338889</t>
+          <t>338978</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>355601</t>
+          <t>355317</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>636</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7095</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>6525</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>79545</t>
+          <t>80077</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>90611</t>
+          <t>90672</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>102392</t>
+          <t>102241</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>112819</t>
+          <t>112355</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>185424</t>
+          <t>186514</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>200611</t>
+          <t>200604</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2899</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,42 +4423,42 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>6011</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
           <t>4,47%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>2173</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>5854</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>63039</t>
+          <t>62614</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>68762</t>
+          <t>68739</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>57066</t>
+          <t>57317</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>63052</t>
+          <t>63448</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>122093</t>
+          <t>122869</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>130970</t>
+          <t>131203</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>5688</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>14823</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5830</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15574</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>26196</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17728</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,42 +4987,42 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>18817</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>13143</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>27152</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
           <t>1,07%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>18817</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>12625</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>27090</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>12826</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>27111</t>
+          <t>26681</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>13400</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>28395</t>
+          <t>27895</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>29928</t>
+          <t>29927</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>49803</t>
+          <t>49987</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5879</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>17936</t>
+          <t>17499</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>527750</t>
+          <t>529752</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>550075</t>
+          <t>552686</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>572490</t>
+          <t>573393</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>594885</t>
+          <t>595419</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1108759</t>
+          <t>1109134</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1141457</t>
+          <t>1139545</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>654</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>579</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70501</t>
+          <t>70689</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79789</t>
+          <t>79601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68889</t>
+          <t>68699</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76009</t>
+          <t>76511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142451</t>
+          <t>142578</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154733</t>
+          <t>154723</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>5562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3837</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71111</t>
+          <t>71501</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79748</t>
+          <t>79899</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80806</t>
+          <t>80938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87855</t>
+          <t>87809</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>155273</t>
+          <t>155448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166447</t>
+          <t>166151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -7257,7 +7257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>594</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69982</t>
+          <t>68969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77575</t>
+          <t>77196</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>70109</t>
+          <t>70567</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77112</t>
+          <t>77129</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>142675</t>
+          <t>143478</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>153136</t>
+          <t>153276</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8488</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13237</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>2825</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10483</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>10628</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>157739</t>
+          <t>158584</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>170451</t>
+          <t>170296</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>183694</t>
+          <t>183454</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>195819</t>
+          <t>195680</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>346522</t>
+          <t>345833</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>363479</t>
+          <t>363327</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>604</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>748</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8621,7 +8621,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8636,42 +8636,42 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>4136</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>8612</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>3,22%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>4136</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1898</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>8480</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6753</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>14445</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11903</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17466</t>
+          <t>17737</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>116764</t>
+          <t>117165</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>129059</t>
+          <t>128749</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>109431</t>
+          <t>109581</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>120741</t>
+          <t>120758</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>229738</t>
+          <t>229212</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>246093</t>
+          <t>245956</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>41487</t>
+          <t>41522</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>47617</t>
+          <t>47610</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>61467</t>
+          <t>61536</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>105935</t>
+          <t>104926</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>112844</t>
+          <t>112610</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>18317</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17284</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>15560</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>30689</t>
+          <t>31364</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>15902</t>
+          <t>15577</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2748</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>22517</t>
+          <t>23235</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>12114</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>25630</t>
+          <t>25745</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>18332</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>21362</t>
+          <t>22144</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>39655</t>
+          <t>39593</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9673</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>22061</t>
+          <t>22299</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>24377</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>39867</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>548139</t>
+          <t>548595</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>570687</t>
+          <t>571140</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>593081</t>
+          <t>592824</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>613995</t>
+          <t>614296</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1147043</t>
+          <t>1147246</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1178838</t>
+          <t>1179125</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3860</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3197</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>544</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4345</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65472</t>
+          <t>65242</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72050</t>
+          <t>72001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72774</t>
+          <t>72940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81733</t>
+          <t>81976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141317</t>
+          <t>140508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>152301</t>
+          <t>151869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5397</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>547</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>79117</t>
+          <t>79579</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87667</t>
+          <t>88086</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89933</t>
+          <t>89776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98629</t>
+          <t>98594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171884</t>
+          <t>172535</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>184426</t>
+          <t>184320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9871</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11388</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46591</t>
+          <t>46363</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54262</t>
+          <t>54339</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55503</t>
+          <t>55328</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64594</t>
+          <t>63939</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104945</t>
+          <t>104991</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116888</t>
+          <t>116615</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4766</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>564</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10588</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15699</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,7 +13105,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>27769</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>179230</t>
+          <t>178673</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191855</t>
+          <t>191143</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>170626</t>
+          <t>170350</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>183632</t>
+          <t>183260</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>354374</t>
+          <t>354950</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>373113</t>
+          <t>373102</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13496,7 +13496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>730</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13633</t>
+          <t>13226</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13855,7 +13855,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1640</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>111615</t>
+          <t>111373</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>122830</t>
+          <t>122589</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>123827</t>
+          <t>124051</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>132029</t>
+          <t>132012</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>239342</t>
+          <t>239038</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>252666</t>
+          <t>252464</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>788</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7479</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>43010</t>
+          <t>43328</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>51909</t>
+          <t>52112</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>54670</t>
+          <t>55095</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>61763</t>
+          <t>62076</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>102013</t>
+          <t>101835</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>112836</t>
+          <t>112184</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>843</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>13263</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9916</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>22579</t>
+          <t>23346</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>21318</t>
+          <t>21901</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>21520</t>
+          <t>21330</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>40170</t>
+          <t>39066</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>17051</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>32849</t>
+          <t>32256</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>20954</t>
+          <t>20575</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>38457</t>
+          <t>38870</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>41229</t>
+          <t>41918</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>63493</t>
+          <t>66044</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>545862</t>
+          <t>547446</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>568487</t>
+          <t>569078</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>587891</t>
+          <t>587242</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>610481</t>
+          <t>609088</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1143405</t>
+          <t>1141970</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1173770</t>
+          <t>1174563</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
